--- a/data/finance.xlsx
+++ b/data/finance.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" customWidth="1" min="1" max="1"/>
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>174.78</v>
+        <v>174.67</v>
       </c>
       <c r="C2">
         <f>(B2/B6-1)*100</f>
@@ -490,11 +490,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>171.9</v>
+        <v>174.78</v>
       </c>
       <c r="C3">
         <f>(B3/B7-1)*100</f>
@@ -504,11 +504,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>173.07</v>
+        <v>171.9</v>
       </c>
       <c r="C4">
         <f>(B4/B8-1)*100</f>
@@ -518,49 +518,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>173.07</v>
+      </c>
+      <c r="C5">
+        <f>(B5/B9-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>174.4</v>
       </c>
-      <c r="C5">
-        <f>(B5/B9-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>174.4</v>
-      </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <f>(B6/B10-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45473</v>
+        <v>45565</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>175.4</v>
+        <v>174.4</v>
       </c>
       <c r="C7" s="7">
         <f>(B7/B11-1)*100</f>
         <v/>
       </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>175.1</v>
+        <v>175.4</v>
       </c>
       <c r="C8" s="7">
         <f>(B8/B12-1)*100</f>
@@ -571,10 +571,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>178.22</v>
+        <v>175.1</v>
       </c>
       <c r="C9" s="7">
         <f>(B9/B13-1)*100</f>
@@ -585,10 +585,10 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>179.3</v>
+        <v>178.22</v>
       </c>
       <c r="C10" s="7">
         <f>(B10/B14-1)*100</f>
@@ -599,10 +599,10 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45107</v>
+        <v>45199</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>180.16</v>
+        <v>179.3</v>
       </c>
       <c r="C11" s="7">
         <f>(B11/B15-1)*100</f>
@@ -613,10 +613,10 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45016</v>
+        <v>45107</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>180.22</v>
+        <v>180.16</v>
       </c>
       <c r="C12" s="7">
         <f>(B12/B16-1)*100</f>
@@ -627,10 +627,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44926</v>
+        <v>45016</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>181.88</v>
+        <v>180.22</v>
       </c>
       <c r="C13" s="7">
         <f>(B13/B17-1)*100</f>
@@ -641,10 +641,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44834</v>
+        <v>44926</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>184.52</v>
+        <v>181.88</v>
       </c>
       <c r="C14" s="7">
         <f>(B14/B18-1)*100</f>
@@ -655,10 +655,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44742</v>
+        <v>44834</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>184.22</v>
+        <v>184.52</v>
       </c>
       <c r="C15" s="7">
         <f>(B15/B19-1)*100</f>
@@ -669,10 +669,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44651</v>
+        <v>44742</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>181.06</v>
+        <v>184.22</v>
       </c>
       <c r="C16" s="7">
         <f>(B16/B20-1)*100</f>
@@ -683,10 +683,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44561</v>
+        <v>44651</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>179.7</v>
+        <v>181.06</v>
       </c>
       <c r="C17" s="7">
         <f>(B17/B21-1)*100</f>
@@ -697,10 +697,10 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44469</v>
+        <v>44561</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>177.99</v>
+        <v>179.7</v>
       </c>
       <c r="C18" s="7">
         <f>(B18/B22-1)*100</f>
@@ -711,10 +711,10 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44377</v>
+        <v>44469</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>175.6</v>
+        <v>177.99</v>
       </c>
       <c r="C19" s="7">
         <f>(B19/B23-1)*100</f>
@@ -725,10 +725,10 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44286</v>
+        <v>44377</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>170.27</v>
+        <v>175.6</v>
       </c>
       <c r="C20" s="7">
         <f>(B20/B24-1)*100</f>
@@ -739,22 +739,24 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>44196</v>
-      </c>
-      <c r="B21" s="7" t="n">
-        <v>173.11</v>
+        <v>44286</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>170.27</v>
       </c>
       <c r="C21" s="7">
         <f>(B21/B25-1)*100</f>
         <v/>
       </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>44104</v>
+        <v>44196</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>172.98</v>
+        <v>173.11</v>
       </c>
       <c r="C22" s="7">
         <f>(B22/B26-1)*100</f>
@@ -763,10 +765,10 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>44012</v>
+        <v>44104</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>173.38</v>
+        <v>172.98</v>
       </c>
       <c r="C23" s="7">
         <f>(B23/B27-1)*100</f>
@@ -775,10 +777,10 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>43921</v>
+        <v>44012</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>177.25</v>
+        <v>173.38</v>
       </c>
       <c r="C24" s="7">
         <f>(B24/B28-1)*100</f>
@@ -787,10 +789,10 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>43830</v>
+        <v>43921</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>178.77</v>
+        <v>177.25</v>
       </c>
       <c r="C25" s="7">
         <f>(B25/B29-1)*100</f>
@@ -799,10 +801,10 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>43738</v>
+        <v>43830</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>179.6</v>
+        <v>178.77</v>
       </c>
       <c r="C26" s="7">
         <f>(B26/B30-1)*100</f>
@@ -811,10 +813,10 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>43646</v>
+        <v>43738</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>179.29</v>
+        <v>179.6</v>
       </c>
       <c r="C27" s="7">
         <f>(B27/B31-1)*100</f>
@@ -823,10 +825,10 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>43555</v>
+        <v>43646</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>178.92</v>
+        <v>179.29</v>
       </c>
       <c r="C28" s="7">
         <f>(B28/B32-1)*100</f>
@@ -835,10 +837,10 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>43465</v>
+        <v>43555</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>180.04</v>
+        <v>178.92</v>
       </c>
       <c r="C29" s="7">
         <f>(B29/B33-1)*100</f>
@@ -847,10 +849,10 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>43373</v>
+        <v>43465</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>179.58</v>
+        <v>180.04</v>
       </c>
       <c r="C30" s="7">
         <f>(B30/B34-1)*100</f>
@@ -859,10 +861,10 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>43281</v>
+        <v>43373</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>178.21</v>
+        <v>179.58</v>
       </c>
       <c r="C31" s="7">
         <f>(B31/B35-1)*100</f>
@@ -871,10 +873,10 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>43190</v>
+        <v>43281</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>177.36</v>
+        <v>178.21</v>
       </c>
       <c r="C32" s="7">
         <f>(B32/B36-1)*100</f>
@@ -883,10 +885,10 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>43100</v>
+        <v>43190</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>178.39</v>
+        <v>177.36</v>
       </c>
       <c r="C33" s="7">
         <f>(B33/B37-1)*100</f>
@@ -895,10 +897,10 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>43008</v>
+        <v>43100</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>179.1</v>
+        <v>178.39</v>
       </c>
       <c r="C34" s="7">
         <f>(B34/B38-1)*100</f>
@@ -907,10 +909,10 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>42916</v>
+        <v>43008</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>179.02</v>
+        <v>179.1</v>
       </c>
       <c r="C35" s="7">
         <f>(B35/B39-1)*100</f>
@@ -919,10 +921,10 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>42825</v>
+        <v>42916</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>177.8</v>
+        <v>179.02</v>
       </c>
       <c r="C36" s="7">
         <f>(B36/B40-1)*100</f>
@@ -931,10 +933,10 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>42735</v>
+        <v>42825</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>178.04</v>
+        <v>177.8</v>
       </c>
       <c r="C37" s="7">
         <f>(B37/B41-1)*100</f>
@@ -943,22 +945,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>42643</v>
+        <v>42735</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>176.96</v>
-      </c>
-      <c r="C38">
+        <v>178.04</v>
+      </c>
+      <c r="C38" s="7">
         <f>(B38/B42-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>42551</v>
+        <v>42643</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>174.78</v>
+        <v>176.96</v>
       </c>
       <c r="C39">
         <f>(B39/B43-1)*100</f>
@@ -967,10 +969,10 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>42460</v>
+        <v>42551</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>171.24</v>
+        <v>174.78</v>
       </c>
       <c r="C40">
         <f>(B40/B44-1)*100</f>
@@ -979,10 +981,10 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>42369</v>
+        <v>42460</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>169.48</v>
+        <v>171.24</v>
       </c>
       <c r="C41">
         <f>(B41/B45-1)*100</f>
@@ -990,7 +992,19 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="7" t="n"/>
+      <c r="A42" s="1" t="n">
+        <v>42369</v>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>169.48</v>
+      </c>
+      <c r="C42">
+        <f>(B42/B46-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/finance.xlsx
+++ b/data/finance.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" customWidth="1" min="1" max="1"/>
@@ -476,11 +476,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>174.67</v>
+        <v>174.9</v>
       </c>
       <c r="C2">
         <f>(B2/B6-1)*100</f>
@@ -490,11 +490,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174.78</v>
+        <v>174.67</v>
       </c>
       <c r="C3">
         <f>(B3/B7-1)*100</f>
@@ -504,11 +504,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171.9</v>
+        <v>174.78</v>
       </c>
       <c r="C4">
         <f>(B4/B8-1)*100</f>
@@ -518,11 +518,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>173.07</v>
+        <v>171.9</v>
       </c>
       <c r="C5">
         <f>(B5/B9-1)*100</f>
@@ -532,49 +532,49 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>173.07</v>
+      </c>
+      <c r="C6">
+        <f>(B6/B10-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>174.4</v>
       </c>
-      <c r="C6">
-        <f>(B6/B10-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>174.4</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <f>(B7/B11-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45473</v>
+        <v>45565</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>175.4</v>
+        <v>174.4</v>
       </c>
       <c r="C8" s="7">
         <f>(B8/B12-1)*100</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>175.1</v>
+        <v>175.4</v>
       </c>
       <c r="C9" s="7">
         <f>(B9/B13-1)*100</f>
@@ -585,10 +585,10 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>178.22</v>
+        <v>175.1</v>
       </c>
       <c r="C10" s="7">
         <f>(B10/B14-1)*100</f>
@@ -599,10 +599,10 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>179.3</v>
+        <v>178.22</v>
       </c>
       <c r="C11" s="7">
         <f>(B11/B15-1)*100</f>
@@ -613,10 +613,10 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45107</v>
+        <v>45199</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>180.16</v>
+        <v>179.3</v>
       </c>
       <c r="C12" s="7">
         <f>(B12/B16-1)*100</f>
@@ -627,10 +627,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45016</v>
+        <v>45107</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>180.22</v>
+        <v>180.16</v>
       </c>
       <c r="C13" s="7">
         <f>(B13/B17-1)*100</f>
@@ -641,10 +641,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44926</v>
+        <v>45016</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>181.88</v>
+        <v>180.22</v>
       </c>
       <c r="C14" s="7">
         <f>(B14/B18-1)*100</f>
@@ -655,10 +655,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44834</v>
+        <v>44926</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>184.52</v>
+        <v>181.88</v>
       </c>
       <c r="C15" s="7">
         <f>(B15/B19-1)*100</f>
@@ -669,10 +669,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44742</v>
+        <v>44834</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>184.22</v>
+        <v>184.52</v>
       </c>
       <c r="C16" s="7">
         <f>(B16/B20-1)*100</f>
@@ -683,10 +683,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44651</v>
+        <v>44742</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>181.06</v>
+        <v>184.22</v>
       </c>
       <c r="C17" s="7">
         <f>(B17/B21-1)*100</f>
@@ -697,10 +697,10 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44561</v>
+        <v>44651</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>179.7</v>
+        <v>181.06</v>
       </c>
       <c r="C18" s="7">
         <f>(B18/B22-1)*100</f>
@@ -711,10 +711,10 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44469</v>
+        <v>44561</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>177.99</v>
+        <v>179.7</v>
       </c>
       <c r="C19" s="7">
         <f>(B19/B23-1)*100</f>
@@ -725,10 +725,10 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44377</v>
+        <v>44469</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>175.6</v>
+        <v>177.99</v>
       </c>
       <c r="C20" s="7">
         <f>(B20/B24-1)*100</f>
@@ -739,10 +739,10 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>44286</v>
+        <v>44377</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>170.27</v>
+        <v>175.6</v>
       </c>
       <c r="C21" s="7">
         <f>(B21/B25-1)*100</f>
@@ -753,22 +753,24 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>44196</v>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>173.11</v>
+        <v>44286</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>170.27</v>
       </c>
       <c r="C22" s="7">
         <f>(B22/B26-1)*100</f>
         <v/>
       </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>44104</v>
+        <v>44196</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>172.98</v>
+        <v>173.11</v>
       </c>
       <c r="C23" s="7">
         <f>(B23/B27-1)*100</f>
@@ -777,10 +779,10 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>44012</v>
+        <v>44104</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>173.38</v>
+        <v>172.98</v>
       </c>
       <c r="C24" s="7">
         <f>(B24/B28-1)*100</f>
@@ -789,10 +791,10 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>43921</v>
+        <v>44012</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>177.25</v>
+        <v>173.38</v>
       </c>
       <c r="C25" s="7">
         <f>(B25/B29-1)*100</f>
@@ -801,10 +803,10 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>43830</v>
+        <v>43921</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>178.77</v>
+        <v>177.25</v>
       </c>
       <c r="C26" s="7">
         <f>(B26/B30-1)*100</f>
@@ -813,10 +815,10 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>43738</v>
+        <v>43830</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>179.6</v>
+        <v>178.77</v>
       </c>
       <c r="C27" s="7">
         <f>(B27/B31-1)*100</f>
@@ -825,10 +827,10 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>43646</v>
+        <v>43738</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>179.29</v>
+        <v>179.6</v>
       </c>
       <c r="C28" s="7">
         <f>(B28/B32-1)*100</f>
@@ -837,10 +839,10 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>43555</v>
+        <v>43646</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>178.92</v>
+        <v>179.29</v>
       </c>
       <c r="C29" s="7">
         <f>(B29/B33-1)*100</f>
@@ -849,10 +851,10 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>43465</v>
+        <v>43555</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>180.04</v>
+        <v>178.92</v>
       </c>
       <c r="C30" s="7">
         <f>(B30/B34-1)*100</f>
@@ -861,10 +863,10 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>43373</v>
+        <v>43465</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>179.58</v>
+        <v>180.04</v>
       </c>
       <c r="C31" s="7">
         <f>(B31/B35-1)*100</f>
@@ -873,10 +875,10 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>43281</v>
+        <v>43373</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>178.21</v>
+        <v>179.58</v>
       </c>
       <c r="C32" s="7">
         <f>(B32/B36-1)*100</f>
@@ -885,10 +887,10 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>43190</v>
+        <v>43281</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>177.36</v>
+        <v>178.21</v>
       </c>
       <c r="C33" s="7">
         <f>(B33/B37-1)*100</f>
@@ -897,10 +899,10 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>43100</v>
+        <v>43190</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>178.39</v>
+        <v>177.36</v>
       </c>
       <c r="C34" s="7">
         <f>(B34/B38-1)*100</f>
@@ -909,10 +911,10 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>43008</v>
+        <v>43100</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>179.1</v>
+        <v>178.39</v>
       </c>
       <c r="C35" s="7">
         <f>(B35/B39-1)*100</f>
@@ -921,10 +923,10 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>42916</v>
+        <v>43008</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>179.02</v>
+        <v>179.1</v>
       </c>
       <c r="C36" s="7">
         <f>(B36/B40-1)*100</f>
@@ -933,10 +935,10 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>42825</v>
+        <v>42916</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>177.8</v>
+        <v>179.02</v>
       </c>
       <c r="C37" s="7">
         <f>(B37/B41-1)*100</f>
@@ -945,10 +947,10 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>42735</v>
+        <v>42825</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>178.04</v>
+        <v>177.8</v>
       </c>
       <c r="C38" s="7">
         <f>(B38/B42-1)*100</f>
@@ -957,22 +959,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>42643</v>
+        <v>42735</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>176.96</v>
-      </c>
-      <c r="C39">
+        <v>178.04</v>
+      </c>
+      <c r="C39" s="7">
         <f>(B39/B43-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>42551</v>
+        <v>42643</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>174.78</v>
+        <v>176.96</v>
       </c>
       <c r="C40">
         <f>(B40/B44-1)*100</f>
@@ -981,10 +983,10 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>42460</v>
+        <v>42551</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>171.24</v>
+        <v>174.78</v>
       </c>
       <c r="C41">
         <f>(B41/B45-1)*100</f>
@@ -993,10 +995,10 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>42369</v>
+        <v>42460</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>169.48</v>
+        <v>171.24</v>
       </c>
       <c r="C42">
         <f>(B42/B46-1)*100</f>
@@ -1004,7 +1006,19 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="7" t="n"/>
+      <c r="A43" s="1" t="n">
+        <v>42369</v>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>169.48</v>
+      </c>
+      <c r="C43">
+        <f>(B43/B47-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
